--- a/result/SMAD7_LUSC_Tables.xlsx
+++ b/result/SMAD7_LUSC_Tables.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Table 2 (Correlation)" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Table 3 (Cox)" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Table 4 (Multivariate OLS)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Table 5 (KM Log-rank)" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,17 +438,18 @@
           <t>Clinical Characteristics</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr"/>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>P-value</t>
         </is>
@@ -462,6 +464,7 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -470,14 +473,17 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
         <v>78</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>111</v>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>0.003</t>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.006</t>
         </is>
       </c>
     </row>
@@ -488,12 +494,15 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="n">
         <v>166</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>132</v>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -504,6 +513,7 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -515,11 +525,14 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
         <v>1</v>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>0.048</t>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.170</t>
         </is>
       </c>
     </row>
@@ -530,12 +543,15 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
         <v>74</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>52</v>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -544,12 +560,15 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
         <v>170</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>191</v>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -560,6 +579,7 @@
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -568,14 +588,17 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
         <v>128</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>110</v>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>0.324</t>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0.472</t>
         </is>
       </c>
     </row>
@@ -586,12 +609,15 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
         <v>69</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>86</v>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -600,12 +626,15 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" t="n">
         <v>40</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>43</v>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -614,12 +643,15 @@
         </is>
       </c>
       <c r="B13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" t="n">
         <v>4</v>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" t="n">
         <v>3</v>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -630,6 +662,7 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -638,14 +671,17 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="n">
         <v>199</v>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" t="n">
         <v>201</v>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>0.995</t>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0.919</t>
         </is>
       </c>
     </row>
@@ -656,12 +692,15 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="n">
         <v>4</v>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" t="n">
         <v>3</v>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -672,6 +711,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -680,14 +720,17 @@
         </is>
       </c>
       <c r="B18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" t="n">
         <v>167</v>
       </c>
-      <c r="C18" t="n">
+      <c r="D18" t="n">
         <v>144</v>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>0.076</t>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0.138</t>
         </is>
       </c>
     </row>
@@ -698,12 +741,15 @@
         </is>
       </c>
       <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="n">
         <v>50</v>
       </c>
-      <c r="C19" t="n">
+      <c r="D19" t="n">
         <v>75</v>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -712,12 +758,15 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>20</v>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="n">
+        <v>20</v>
+      </c>
+      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -726,12 +775,15 @@
         </is>
       </c>
       <c r="B21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" t="n">
         <v>2</v>
       </c>
-      <c r="C21" t="n">
+      <c r="D21" t="n">
         <v>3</v>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -742,6 +794,7 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -750,14 +803,17 @@
         </is>
       </c>
       <c r="B23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" t="n">
         <v>66</v>
       </c>
-      <c r="C23" t="n">
+      <c r="D23" t="n">
         <v>43</v>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>0.052</t>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0.208</t>
         </is>
       </c>
     </row>
@@ -768,12 +824,15 @@
         </is>
       </c>
       <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="n">
         <v>132</v>
       </c>
-      <c r="C24" t="n">
+      <c r="D24" t="n">
         <v>153</v>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -782,12 +841,15 @@
         </is>
       </c>
       <c r="B25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" t="n">
         <v>37</v>
       </c>
-      <c r="C25" t="n">
+      <c r="D25" t="n">
         <v>33</v>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -796,12 +858,15 @@
         </is>
       </c>
       <c r="B26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" t="n">
         <v>9</v>
       </c>
-      <c r="C26" t="n">
+      <c r="D26" t="n">
         <v>14</v>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -812,6 +877,7 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -820,14 +886,17 @@
         </is>
       </c>
       <c r="B28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" t="n">
         <v>34</v>
       </c>
-      <c r="C28" t="n">
+      <c r="D28" t="n">
         <v>42</v>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>0.382</t>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0.553</t>
         </is>
       </c>
     </row>
@@ -838,12 +907,15 @@
         </is>
       </c>
       <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="n">
         <v>210</v>
       </c>
-      <c r="C29" t="n">
+      <c r="D29" t="n">
         <v>202</v>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -882,32 +954,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>TP53Expression</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>CDKN2AExpression</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>SOX2Expression</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>PIK3CAExpression</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>NOTCH1Expression</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>age</t>
         </is>
       </c>
     </row>
@@ -934,32 +1006,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>0.101</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>-0.006</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>-0.114</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>-0.302</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>-0.213</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>0.121</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0.101</t>
         </is>
       </c>
     </row>
@@ -978,32 +1050,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>0.041</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>0.900</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>0.021</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>0.015</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.041</t>
         </is>
       </c>
     </row>
@@ -1030,32 +1102,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>0.041</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>-0.008</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>-0.022</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>-0.040</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>0.021</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>0.003</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0.041</t>
         </is>
       </c>
     </row>
@@ -1074,39 +1146,39 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
+          <t>0.413</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>0.871</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>0.658</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>0.415</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>0.671</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>0.957</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0.413</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TP53Expression</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1116,12 +1188,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.006</t>
+          <t>0.101</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.008</t>
+          <t>0.041</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1131,27 +1203,27 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.012</t>
+          <t>-0.047</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>-0.009</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>-0.147</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>-0.033</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-0.047</t>
+          <t>0.001</t>
         </is>
       </c>
     </row>
@@ -1164,45 +1236,45 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.900</t>
+          <t>0.041</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.871</t>
+          <t>0.413</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.808</t>
+          <t>0.345</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>0.864</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>0.003</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>0.511</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.345</t>
+          <t>0.978</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CDKN2AExpression</t>
+          <t>TP53Expression</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1212,42 +1284,42 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.114</t>
+          <t>-0.006</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-0.022</t>
+          <t>-0.008</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>-0.047</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>-0.012</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>-0.005</t>
-        </is>
-      </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.026</t>
+          <t>0.069</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.070</t>
+          <t>0.063</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-0.009</t>
+          <t>0.095</t>
         </is>
       </c>
     </row>
@@ -1260,45 +1332,45 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>0.900</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.658</t>
+          <t>0.871</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.808</t>
+          <t>0.345</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.920</t>
+          <t>0.808</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.606</t>
+          <t>0.164</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>0.205</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.864</t>
+          <t>0.054</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SOX2Expression</t>
+          <t>CDKN2AExpression</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1308,42 +1380,42 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.302</t>
+          <t>-0.114</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-0.040</t>
+          <t>-0.022</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>-0.009</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>-0.012</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>-0.005</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0.555</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>-0.026</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-0.147</t>
+          <t>-0.070</t>
         </is>
       </c>
     </row>
@@ -1356,45 +1428,45 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>&lt;0.001</t>
+          <t>0.021</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.415</t>
+          <t>0.658</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>0.864</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.920</t>
+          <t>0.808</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>&lt;0.001</t>
+          <t>0.920</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.788</t>
+          <t>0.606</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.155</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PIK3CAExpression</t>
+          <t>SOX2Expression</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1404,42 +1476,42 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.213</t>
+          <t>-0.302</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>-0.040</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>-0.147</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-0.026</t>
+          <t>0.069</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
+          <t>-0.005</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>0.555</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-0.035</t>
-        </is>
-      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-0.033</t>
+          <t>0.013</t>
         </is>
       </c>
     </row>
@@ -1457,40 +1529,40 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.671</t>
+          <t>0.415</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>0.003</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.606</t>
+          <t>0.164</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>&lt;0.001</t>
+          <t>0.920</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.477</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.511</t>
+          <t>0.788</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NOTCH1Expression</t>
+          <t>PIK3CAExpression</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1500,42 +1572,42 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>-0.213</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.021</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>-0.033</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-0.070</t>
+          <t>0.063</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>-0.026</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
+          <t>0.555</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>-0.035</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>0.001</t>
         </is>
       </c>
     </row>
@@ -1548,45 +1620,45 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.957</t>
+          <t>0.671</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>0.511</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>0.205</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.788</t>
+          <t>0.606</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.477</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.978</t>
+          <t>0.477</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>NOTCH1Expression</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1596,37 +1668,37 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>0.121</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>0.003</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>-0.047</t>
+          <t>0.001</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-0.009</t>
+          <t>0.095</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-0.147</t>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.033</t>
+          <t>0.013</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>-0.035</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1644,37 +1716,37 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>0.015</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.413</t>
+          <t>0.957</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.345</t>
+          <t>0.978</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.864</t>
+          <t>0.054</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.155</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.511</t>
+          <t>0.788</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.978</t>
+          <t>0.477</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -1690,7 +1762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1721,7 +1793,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.030</t>
+          <t>0.032</t>
         </is>
       </c>
     </row>
@@ -1736,82 +1808,172 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.954</t>
+          <t>0.895</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SMAD7group_Low</t>
+          <t>TP53Expression</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.831</v>
+        <v>1</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.228</t>
+          <t>0.788</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>gender_MALE</t>
+          <t>CDKN2AExpression</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.266</v>
+        <v>1</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.190</t>
+          <t>0.864</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pathologic_stage_2.0</t>
+          <t>SOX2Expression</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.049</v>
+        <v>1</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.789</t>
+          <t>0.145</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>pathologic_stage_3.0</t>
+          <t>PIK3CAExpression</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.358</v>
+        <v>1</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.130</t>
+          <t>0.423</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>NOTCH1Expression</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0.979</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SMAD7group_High</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>203294.093</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0.995</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SMAD7group_Low</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>177752.268</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0.995</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>gender_MALE</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0.212</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>pathologic_stage_2.0</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.102</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0.591</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>pathologic_stage_3.0</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.404</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0.097</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>pathologic_stage_4.0</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>3.123</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>0.015</t>
+      <c r="B14" t="n">
+        <v>3.187</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0.014</t>
         </is>
       </c>
     </row>
@@ -2757,4 +2919,99 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Survival Type</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Cancer Type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Chi-square</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>P-value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Overall Survival (OS)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>LUSC</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>SMAD7</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>4.537</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.103</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Relapse-Free Survival (RFS)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>LUSC</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SMAD7</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1.168</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.280</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/result/SMAD7_LUSC_Tables.xlsx
+++ b/result/SMAD7_LUSC_Tables.xlsx
@@ -1001,37 +1001,37 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.030</t>
+          <t>0.035</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>0.103</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-0.006</t>
+          <t>-0.016</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-0.114</t>
+          <t>-0.118</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-0.302</t>
+          <t>-0.305</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.213</t>
+          <t>-0.225</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>0.113</t>
         </is>
       </c>
     </row>
@@ -1045,22 +1045,22 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.546</t>
+          <t>0.481</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>0.022</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.900</t>
+          <t>0.720</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>0.009</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>0.013</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.030</t>
+          <t>0.035</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1102,17 +1102,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>0.045</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.008</t>
+          <t>-0.012</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.022</t>
+          <t>-0.021</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>0.018</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.001</t>
         </is>
       </c>
     </row>
@@ -1140,23 +1140,23 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.546</t>
+          <t>0.481</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.413</t>
+          <t>0.359</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.871</t>
+          <t>0.802</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.658</t>
+          <t>0.675</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1166,12 +1166,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.671</t>
+          <t>0.717</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.957</t>
+          <t>0.981</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>0.103</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>0.045</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1203,27 +1203,27 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.047</t>
+          <t>-0.045</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-0.009</t>
+          <t>-0.012</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.147</t>
+          <t>-0.116</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.033</t>
+          <t>-0.025</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>-0.012</t>
         </is>
       </c>
     </row>
@@ -1236,38 +1236,38 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>0.022</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.413</t>
+          <t>0.359</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.345</t>
+          <t>0.326</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.864</t>
+          <t>0.788</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.011</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.511</t>
+          <t>0.584</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.978</t>
+          <t>0.785</t>
         </is>
       </c>
     </row>
@@ -1284,17 +1284,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.006</t>
+          <t>-0.016</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-0.008</t>
+          <t>-0.012</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-0.047</t>
+          <t>-0.045</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1304,22 +1304,22 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-0.012</t>
+          <t>-0.011</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>0.058</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>0.050</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>0.196</t>
         </is>
       </c>
     </row>
@@ -1332,38 +1332,38 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.900</t>
+          <t>0.720</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.871</t>
+          <t>0.802</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.345</t>
+          <t>0.326</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.808</t>
+          <t>0.810</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>0.200</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>0.273</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
     </row>
@@ -1380,22 +1380,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.114</t>
+          <t>-0.118</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-0.022</t>
+          <t>-0.021</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-0.009</t>
+          <t>-0.012</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-0.012</t>
+          <t>-0.011</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1405,17 +1405,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.005</t>
+          <t>-0.004</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.026</t>
+          <t>-0.014</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-0.070</t>
+          <t>-0.074</t>
         </is>
       </c>
     </row>
@@ -1428,38 +1428,38 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>0.009</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.658</t>
+          <t>0.675</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.864</t>
+          <t>0.788</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.808</t>
+          <t>0.810</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.920</t>
+          <t>0.929</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.606</t>
+          <t>0.761</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>0.104</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.302</t>
+          <t>-0.305</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1486,17 +1486,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-0.147</t>
+          <t>-0.116</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>0.058</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-0.005</t>
+          <t>-0.004</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1506,12 +1506,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.555</t>
+          <t>0.528</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>0.004</t>
         </is>
       </c>
     </row>
@@ -1534,17 +1534,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.011</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>0.200</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.920</t>
+          <t>0.929</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.788</t>
+          <t>0.933</t>
         </is>
       </c>
     </row>
@@ -1572,32 +1572,32 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.213</t>
+          <t>-0.225</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>0.018</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>-0.033</t>
+          <t>-0.025</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>0.050</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-0.026</t>
+          <t>-0.014</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.555</t>
+          <t>0.528</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-0.035</t>
+          <t>-0.032</t>
         </is>
       </c>
     </row>
@@ -1625,22 +1625,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.671</t>
+          <t>0.717</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.511</t>
+          <t>0.584</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>0.273</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.606</t>
+          <t>0.761</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1651,7 +1651,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.477</t>
+          <t>0.482</t>
         </is>
       </c>
     </row>
@@ -1668,37 +1668,37 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>0.113</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.001</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>-0.012</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>0.196</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-0.070</t>
+          <t>-0.074</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>0.004</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.035</t>
+          <t>-0.032</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1716,37 +1716,37 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>0.013</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.957</t>
+          <t>0.981</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.978</t>
+          <t>0.785</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>0.104</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.788</t>
+          <t>0.933</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.477</t>
+          <t>0.482</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>

--- a/result/SMAD7_LUSC_Tables.xlsx
+++ b/result/SMAD7_LUSC_Tables.xlsx
@@ -1039,7 +1039,7 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
@@ -1135,7 +1135,7 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1231,7 +1231,7 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1327,7 +1327,7 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1423,7 +1423,7 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1519,7 +1519,7 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1615,7 +1615,7 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1711,7 +1711,7 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
